--- a/branches/main/StructureDefinition-mii-pr-icu-bilanz-ausfuhr-magensonde.xlsx
+++ b/branches/main/StructureDefinition-mii-pr-icu-bilanz-ausfuhr-magensonde.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T11:25:36+00:00</t>
+    <t>2026-10-21T14:50:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/main/StructureDefinition-mii-pr-icu-bilanz-ausfuhr-magensonde.xlsx
+++ b/branches/main/StructureDefinition-mii-pr-icu-bilanz-ausfuhr-magensonde.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.3</t>
+    <t>2027.0.0-ballot.3-rc.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:50:03+00:00</t>
+    <t>2026-10-30T08:50:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -7492,7 +7492,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
         <v>309</v>
       </c>
@@ -7511,7 +7511,7 @@
         <v>90</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>80</v>
@@ -8432,7 +8432,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
         <v>322</v>
       </c>
@@ -8451,7 +8451,7 @@
         <v>90</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>80</v>
